--- a/Parcial 1/G6_Matriz_IREB_V2_AlaSynk.xlsx
+++ b/Parcial 1/G6_Matriz_IREB_V2_AlaSynk.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfon\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UNIVERSIDAD\IngenieriaSoftware\6TO SEMESTRE\G6_Analisis\ChuquiKerly_36838_G6_ADSW\Parcial 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E133EF-DE13-4096-B3C5-8D5C066C77FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF33D17-2586-4985-A5CE-E02E11F42A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matriz Ckeck LIst" sheetId="1" r:id="rId1"/>
@@ -415,7 +415,7 @@
     <comment ref="F8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Acuerdo y aprobación del cliente confirmados por el equipo. Falta evidencia documental.</t>
       </text>
@@ -423,7 +423,7 @@
     <comment ref="I8" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Acuerdo y aprobación del cliente confirmados por el equipo. Falta evidencia documental.</t>
       </text>
@@ -431,7 +431,7 @@
     <comment ref="K8" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0100-000017000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Acuerdo y aprobación del cliente confirmados por el equipo. Falta evidencia documental.</t>
       </text>
@@ -439,7 +439,7 @@
     <comment ref="F9" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, el requisito tiene importancia alta.</t>
       </text>
@@ -447,7 +447,7 @@
     <comment ref="I9" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, el requisito tiene importancia alta.</t>
       </text>
@@ -455,7 +455,7 @@
     <comment ref="K9" authorId="5" shapeId="0" xr:uid="{00000000-0006-0000-0100-000018000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, el requisito tiene importancia alta.</t>
       </text>
@@ -463,7 +463,7 @@
     <comment ref="F10" authorId="6" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, están definidos el ingreso por credenciales, la sesión y su cierre.</t>
       </text>
@@ -471,7 +471,7 @@
     <comment ref="I10" authorId="7" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, falta precisar los campos y la autorización de cada operación.</t>
       </text>
@@ -479,7 +479,7 @@
     <comment ref="K10" authorId="8" shapeId="0" xr:uid="{00000000-0006-0000-0100-000019000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, falta precisar la correspondencia entre roles, operaciones, sucursales y plan.</t>
       </text>
@@ -487,7 +487,7 @@
     <comment ref="F11" authorId="9" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El equipo confirma los cambios. Falta documentar las decisiones y el historial de revisión.</t>
       </text>
@@ -495,7 +495,7 @@
     <comment ref="I11" authorId="10" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000F000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El equipo confirma los cambios. Falta documentar las decisiones y el historial de revisión.</t>
       </text>
@@ -503,7 +503,7 @@
     <comment ref="K11" authorId="11" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001A000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El equipo confirma los cambios. Falta documentar las decisiones y el historial de revisión.</t>
       </text>
@@ -511,7 +511,7 @@
     <comment ref="F12" authorId="12" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, protege el acceso individual a los módulos y datos.</t>
       </text>
@@ -519,7 +519,7 @@
     <comment ref="I12" authorId="13" shapeId="0" xr:uid="{00000000-0006-0000-0100-000010000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, organiza clínica y sucursales para los módulos autorizados.</t>
       </text>
@@ -527,7 +527,7 @@
     <comment ref="K12" authorId="14" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001B000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, limita el acceso mediante cuentas, roles y permisos.</t>
       </text>
@@ -535,7 +535,7 @@
     <comment ref="F13" authorId="15" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS y los casos de uso, no se detectaron contradicciones en el alcance revisado.</t>
       </text>
@@ -543,7 +543,7 @@
     <comment ref="I13" authorId="16" shapeId="0" xr:uid="{00000000-0006-0000-0100-000011000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Falta precisar los permisos por operación y conciliar su descripción con la implementación.</t>
       </text>
@@ -551,7 +551,7 @@
     <comment ref="K13" authorId="17" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001C000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS y los casos de uso, no se detectaron contradicciones en el alcance revisado.</t>
       </text>
@@ -559,7 +559,7 @@
     <comment ref="F14" authorId="18" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS y las historias, hay criterios observables. Faltan pruebas formales ejecutadas.</t>
       </text>
@@ -567,7 +567,7 @@
     <comment ref="I14" authorId="19" shapeId="0" xr:uid="{00000000-0006-0000-0100-000012000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS y las historias, hay criterios observables. Faltan pruebas formales ejecutadas.</t>
       </text>
@@ -575,7 +575,7 @@
     <comment ref="K14" authorId="20" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001D000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS y las historias, hay criterios observables. Faltan pruebas formales ejecutadas.</t>
       </text>
@@ -583,7 +583,7 @@
     <comment ref="F15" authorId="21" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el código, la función está implementada. No se verificó su funcionamiento en producción.</t>
       </text>
@@ -591,7 +591,7 @@
     <comment ref="I15" authorId="22" shapeId="0" xr:uid="{00000000-0006-0000-0100-000013000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el código, la función está implementada. No se verificó su funcionamiento en producción.</t>
       </text>
@@ -599,7 +599,7 @@
     <comment ref="K15" authorId="23" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001E000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el código, la función está implementada. No se verificó su funcionamiento en producción.</t>
       </text>
@@ -607,7 +607,7 @@
     <comment ref="F16" authorId="24" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según la matriz actual, existen vínculos entre requisitos, casos e historias. Falta el origen individual y las pruebas.</t>
       </text>
@@ -615,7 +615,7 @@
     <comment ref="I16" authorId="25" shapeId="0" xr:uid="{00000000-0006-0000-0100-000014000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según la matriz actual, existen vínculos entre requisitos, casos e historias. Falta el origen individual y las pruebas.</t>
       </text>
@@ -623,7 +623,7 @@
     <comment ref="K16" authorId="26" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001F000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según la matriz actual, existen vínculos entre requisitos, casos e historias. Falta el origen individual y las pruebas.</t>
       </text>
@@ -631,7 +631,7 @@
     <comment ref="F17" authorId="27" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS y el caso de uso, se incluyen condiciones, resultado, flujos y excepciones.</t>
       </text>
@@ -639,7 +639,7 @@
     <comment ref="I17" authorId="28" shapeId="0" xr:uid="{00000000-0006-0000-0100-000015000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, faltan campos y permisos por operación en la especificación.</t>
       </text>
@@ -647,7 +647,7 @@
     <comment ref="K17" authorId="29" shapeId="0" xr:uid="{00000000-0006-0000-0100-000020000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, falta completar la tabla normativa de autorizaciones.</t>
       </text>
@@ -655,7 +655,7 @@
     <comment ref="F18" authorId="30" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, el glosario y la redacción facilitan comprender el requisito.</t>
       </text>
@@ -663,7 +663,7 @@
     <comment ref="I18" authorId="31" shapeId="0" xr:uid="{00000000-0006-0000-0100-000016000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, el glosario y la redacción facilitan comprender el requisito.</t>
       </text>
@@ -671,7 +671,7 @@
     <comment ref="K18" authorId="32" shapeId="0" xr:uid="{00000000-0006-0000-0100-000021000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, el glosario y la redacción facilitan comprender el requisito.</t>
       </text>
@@ -739,7 +739,7 @@
     <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, el requisito está documentado con alcance, condiciones y criterios de aceptación.</t>
       </text>
@@ -747,7 +747,7 @@
     <comment ref="H8" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000012000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, el requisito está documentado con alcance, condiciones y criterios de aceptación.</t>
       </text>
@@ -755,7 +755,7 @@
     <comment ref="N8" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000023000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, el requisito está documentado con alcance, condiciones y criterios de aceptación.</t>
       </text>
@@ -763,7 +763,7 @@
     <comment ref="B9" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el código, la función está implementada. No se verificó su funcionamiento en producción.</t>
       </text>
@@ -771,7 +771,7 @@
     <comment ref="H9" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0200-000013000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el código, la función está implementada. No se verificó su funcionamiento en producción.</t>
       </text>
@@ -779,7 +779,7 @@
     <comment ref="N9" authorId="5" shapeId="0" xr:uid="{00000000-0006-0000-0200-000024000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el código, la función está implementada. No se verificó su funcionamiento en producción.</t>
       </text>
@@ -787,7 +787,7 @@
     <comment ref="B10" authorId="6" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según la matriz actual, el requisito se relaciona con casos e historias. No acredita trazabilidad histórica.</t>
       </text>
@@ -795,7 +795,7 @@
     <comment ref="H10" authorId="7" shapeId="0" xr:uid="{00000000-0006-0000-0200-000014000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según la matriz actual, el requisito se relaciona con casos e historias. No acredita trazabilidad histórica.</t>
       </text>
@@ -803,7 +803,7 @@
     <comment ref="N10" authorId="8" shapeId="0" xr:uid="{00000000-0006-0000-0200-000025000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según la matriz actual, el requisito se relaciona con casos e historias. No acredita trazabilidad histórica.</t>
       </text>
@@ -811,7 +811,7 @@
     <comment ref="B11" authorId="9" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     No hay registro de la fuente original, la fecha ni el interesado que originó el requisito.</t>
       </text>
@@ -819,7 +819,7 @@
     <comment ref="H11" authorId="10" shapeId="0" xr:uid="{00000000-0006-0000-0200-000015000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     No hay registro de la fuente original, la fecha ni el interesado que originó el requisito.</t>
       </text>
@@ -827,7 +827,7 @@
     <comment ref="N11" authorId="11" shapeId="0" xr:uid="{00000000-0006-0000-0200-000026000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     No hay registro de la fuente original, la fecha ni el interesado que originó el requisito.</t>
       </text>
@@ -835,7 +835,7 @@
     <comment ref="B12" authorId="12" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según la matriz actual, los identificadores permiten volver al requisito desde sus casos e historias.</t>
       </text>
@@ -843,7 +843,7 @@
     <comment ref="H12" authorId="13" shapeId="0" xr:uid="{00000000-0006-0000-0200-000016000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según la matriz actual, los identificadores permiten volver al requisito desde sus casos e historias.</t>
       </text>
@@ -851,7 +851,7 @@
     <comment ref="N12" authorId="14" shapeId="0" xr:uid="{00000000-0006-0000-0200-000027000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según la matriz actual, los identificadores permiten volver al requisito desde sus casos e historias.</t>
       </text>
@@ -859,7 +859,7 @@
     <comment ref="B13" authorId="15" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS y lo confirmado por el equipo, la función responde a una necesidad del cliente.</t>
       </text>
@@ -867,7 +867,7 @@
     <comment ref="H13" authorId="16" shapeId="0" xr:uid="{00000000-0006-0000-0200-000017000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS y lo confirmado por el equipo, la función responde a una necesidad del cliente.</t>
       </text>
@@ -875,7 +875,7 @@
     <comment ref="N13" authorId="17" shapeId="0" xr:uid="{00000000-0006-0000-0200-000028000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS y lo confirmado por el equipo, la función responde a una necesidad del cliente.</t>
       </text>
@@ -883,7 +883,7 @@
     <comment ref="B14" authorId="18" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS y los casos de uso, no se detectaron contradicciones en el alcance revisado.</t>
       </text>
@@ -891,7 +891,7 @@
     <comment ref="H14" authorId="19" shapeId="0" xr:uid="{00000000-0006-0000-0200-000018000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Falta precisar los permisos por operación y conciliar su descripción con la implementación.</t>
       </text>
@@ -899,7 +899,7 @@
     <comment ref="N14" authorId="20" shapeId="0" xr:uid="{00000000-0006-0000-0200-000029000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS y los casos de uso, no se detectaron contradicciones en el alcance revisado.</t>
       </text>
@@ -907,7 +907,7 @@
     <comment ref="B15" authorId="21" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, el requisito contribuye a los objetivos del sistema odontológico.</t>
       </text>
@@ -915,7 +915,7 @@
     <comment ref="H15" authorId="22" shapeId="0" xr:uid="{00000000-0006-0000-0200-000019000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, el requisito contribuye a los objetivos del sistema odontológico.</t>
       </text>
@@ -923,7 +923,7 @@
     <comment ref="N15" authorId="23" shapeId="0" xr:uid="{00000000-0006-0000-0200-00002A000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, el requisito contribuye a los objetivos del sistema odontológico.</t>
       </text>
@@ -931,7 +931,7 @@
     <comment ref="B16" authorId="24" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     No hay un plan de validación con responsable, plazo, presupuesto y casos aprobados.</t>
       </text>
@@ -939,7 +939,7 @@
     <comment ref="H16" authorId="25" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001A000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     No hay un plan de validación con responsable, plazo, presupuesto y casos aprobados.</t>
       </text>
@@ -947,7 +947,7 @@
     <comment ref="N16" authorId="26" shapeId="0" xr:uid="{00000000-0006-0000-0200-00002B000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     No hay un plan de validación con responsable, plazo, presupuesto y casos aprobados.</t>
       </text>
@@ -955,7 +955,7 @@
     <comment ref="B22" authorId="27" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, se usa IEEE 830 como referencia documental.</t>
       </text>
@@ -963,7 +963,7 @@
     <comment ref="H22" authorId="28" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001B000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, se usa IEEE 830 como referencia documental.</t>
       </text>
@@ -971,7 +971,7 @@
     <comment ref="N22" authorId="29" shapeId="0" xr:uid="{00000000-0006-0000-0200-00002C000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, se usa IEEE 830 como referencia documental.</t>
       </text>
@@ -979,7 +979,7 @@
     <comment ref="B23" authorId="30" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000B000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, se incluyen descripción, condiciones, resultado y criterio de aceptación.</t>
       </text>
@@ -987,7 +987,7 @@
     <comment ref="H23" authorId="31" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001C000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, se incluyen descripción, condiciones, resultado y criterio de aceptación.</t>
       </text>
@@ -995,7 +995,7 @@
     <comment ref="N23" authorId="32" shapeId="0" xr:uid="{00000000-0006-0000-0200-00002D000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, se incluyen descripción, condiciones, resultado y criterio de aceptación.</t>
       </text>
@@ -1003,7 +1003,7 @@
     <comment ref="B24" authorId="33" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000C000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, existe un glosario compartido de términos.</t>
       </text>
@@ -1011,7 +1011,7 @@
     <comment ref="H24" authorId="34" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001D000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, existe un glosario compartido de términos.</t>
       </text>
@@ -1019,7 +1019,7 @@
     <comment ref="N24" authorId="35" shapeId="0" xr:uid="{00000000-0006-0000-0200-00002E000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, existe un glosario compartido de términos.</t>
       </text>
@@ -1027,7 +1027,7 @@
     <comment ref="B25" authorId="36" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000D000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS y los casos de uso, el alcance básico tiene una interpretación clara.</t>
       </text>
@@ -1035,7 +1035,7 @@
     <comment ref="H25" authorId="37" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001E000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, falta precisar los campos y la autorización de cada operación.</t>
       </text>
@@ -1043,7 +1043,7 @@
     <comment ref="N25" authorId="38" shapeId="0" xr:uid="{00000000-0006-0000-0200-00002F000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, falta precisar la correspondencia entre roles, operaciones, sucursales y plan.</t>
       </text>
@@ -1051,7 +1051,7 @@
     <comment ref="B26" authorId="39" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Los casos de uso y las historias siguen una estructura uniforme con flujos y criterios.</t>
       </text>
@@ -1059,7 +1059,7 @@
     <comment ref="H26" authorId="40" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001F000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Los casos de uso y las historias siguen una estructura uniforme con flujos y criterios.</t>
       </text>
@@ -1067,7 +1067,7 @@
     <comment ref="N26" authorId="41" shapeId="0" xr:uid="{00000000-0006-0000-0200-000030000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Los casos de uso y las historias siguen una estructura uniforme con flujos y criterios.</t>
       </text>
@@ -1075,7 +1075,7 @@
     <comment ref="B32" authorId="42" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000F000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El equipo confirma el acuerdo y la aprobación del cliente. Falta evidencia documental.</t>
       </text>
@@ -1083,7 +1083,7 @@
     <comment ref="H32" authorId="43" shapeId="0" xr:uid="{00000000-0006-0000-0200-000020000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El equipo confirma el acuerdo y la aprobación del cliente. Falta evidencia documental.</t>
       </text>
@@ -1091,7 +1091,7 @@
     <comment ref="N32" authorId="44" shapeId="0" xr:uid="{00000000-0006-0000-0200-000031000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El equipo confirma el acuerdo y la aprobación del cliente. Falta evidencia documental.</t>
       </text>
@@ -1099,7 +1099,7 @@
     <comment ref="B33" authorId="45" shapeId="0" xr:uid="{00000000-0006-0000-0200-000010000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El equipo confirma que el cliente aprobó las modificaciones actuales. Falta respaldo documental.</t>
       </text>
@@ -1107,7 +1107,7 @@
     <comment ref="H33" authorId="46" shapeId="0" xr:uid="{00000000-0006-0000-0200-000021000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El equipo confirma que el cliente aprobó las modificaciones actuales. Falta respaldo documental.</t>
       </text>
@@ -1115,7 +1115,7 @@
     <comment ref="N33" authorId="47" shapeId="0" xr:uid="{00000000-0006-0000-0200-000032000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El equipo confirma que el cliente aprobó las modificaciones actuales. Falta respaldo documental.</t>
       </text>
@@ -1123,7 +1123,7 @@
     <comment ref="B34" authorId="48" shapeId="0" xr:uid="{00000000-0006-0000-0200-000011000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El equipo confirma que se resolvieron todos los conflictos conocidos. Falta registrar las decisiones.</t>
       </text>
@@ -1131,7 +1131,7 @@
     <comment ref="H34" authorId="49" shapeId="0" xr:uid="{00000000-0006-0000-0200-000022000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El equipo confirma que se resolvieron todos los conflictos conocidos. Falta registrar las decisiones.</t>
       </text>
@@ -1139,7 +1139,7 @@
     <comment ref="N34" authorId="50" shapeId="0" xr:uid="{00000000-0006-0000-0200-000033000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El equipo confirma que se resolvieron todos los conflictos conocidos. Falta registrar las decisiones.</t>
       </text>
@@ -1162,7 +1162,7 @@
     <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El cliente aprobó el requisito, según el equipo. Faltan los entregables y el respaldo formal de la entrevista.</t>
       </text>
@@ -1170,7 +1170,7 @@
     <comment ref="A4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, hay criterios de aceptación. Faltan casos formales con resultados y evidencia de ejecución.</t>
       </text>
@@ -1178,7 +1178,7 @@
     <comment ref="A11" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El cliente aprobó el requisito, según el equipo. Faltan los entregables y el respaldo formal de la entrevista.</t>
       </text>
@@ -1186,7 +1186,7 @@
     <comment ref="A12" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, hay criterios de aceptación. Faltan casos formales con resultados y evidencia de ejecución.</t>
       </text>
@@ -1194,7 +1194,7 @@
     <comment ref="A19" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     El cliente aprobó el requisito, según el equipo. Faltan los entregables y el respaldo formal de la entrevista.</t>
       </text>
@@ -1202,7 +1202,7 @@
     <comment ref="A20" authorId="5" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Según el SRS, hay criterios de aceptación. Faltan casos formales con resultados y evidencia de ejecución.</t>
       </text>
@@ -1543,7 +1543,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1647,18 +1647,8 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="20">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1759,18 +1749,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1978,7 +1956,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2190,20 +2168,20 @@
     <xf numFmtId="0" fontId="10" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2211,53 +2189,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2266,14 +2209,43 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="309">
+  <dxfs count="319">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2298,14 +2270,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
       </font>
       <fill>
@@ -2317,6 +2281,14 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2361,14 +2333,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
       </font>
       <fill>
@@ -2380,6 +2344,14 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2424,14 +2396,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
       </font>
       <fill>
@@ -2443,6 +2407,14 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2487,14 +2459,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
       </font>
       <fill>
@@ -2506,6 +2470,14 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2528,6 +2500,36 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2569,6 +2571,28 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2580,6 +2604,25 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2591,6 +2634,39 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2613,10 +2689,62 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFF0000"/>
       </font>
       <fill>
         <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -2632,6 +2760,25 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2654,14 +2801,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
       </font>
       <fill>
@@ -2673,6 +2812,17 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2684,6 +2834,25 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2695,6 +2864,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2717,6 +2916,25 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
       </font>
       <fill>
@@ -2728,10 +2946,13 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -2758,6 +2979,25 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2780,6 +3020,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
       </font>
       <fill>
@@ -2791,10 +3061,13 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -2821,6 +3094,25 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2832,6 +3124,25 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
       </font>
       <fill>
@@ -2843,6 +3154,28 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2862,14 +3195,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
       </font>
       <fill>
@@ -2903,6 +3228,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2914,6 +3269,28 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2925,6 +3302,22 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
       </font>
       <fill>
@@ -2936,14 +3329,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2955,6 +3340,28 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2966,6 +3373,25 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2977,6 +3403,47 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2988,14 +3455,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3018,6 +3477,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3040,6 +3529,25 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3051,6 +3559,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3062,10 +3600,24 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -3081,6 +3633,17 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
       </font>
       <fill>
@@ -3092,6 +3655,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3103,6 +3696,14 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3114,10 +3715,35 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -3133,6 +3759,14 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3166,6 +3800,28 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
       </font>
       <fill>
@@ -3196,6 +3852,14 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3218,14 +3882,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
       </font>
       <fill>
@@ -3300,6 +3956,14 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
       </font>
       <fill>
@@ -3311,10 +3975,13 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -3341,6 +4008,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3352,6 +4049,47 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3363,6 +4101,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
       </font>
       <fill>
@@ -3374,6 +4142,50 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFF0000"/>
       </font>
       <fill>
@@ -3393,6 +4205,17 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3404,6 +4227,36 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3423,6 +4276,28 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3445,6 +4320,28 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFF0000"/>
       </font>
       <fill>
@@ -3486,14 +4383,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
       </font>
       <fill>
@@ -3505,6 +4394,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3516,6 +4435,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3527,6 +4476,17 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3538,6 +4498,14 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
       </font>
       <fill>
@@ -3549,10 +4517,13 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -3568,6 +4539,25 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3590,6 +4580,39 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFF0000"/>
       </font>
       <fill>
@@ -3609,6 +4632,28 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3620,6 +4665,17 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3631,6 +4687,44 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor indexed="64"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3642,6 +4736,25 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3653,6 +4766,17 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFF0000"/>
       </font>
       <fill>
@@ -3672,6 +4796,17 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3702,6 +4837,17 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3713,6 +4859,25 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3735,6 +4900,17 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3746,6 +4922,36 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3757,6 +4963,36 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3768,14 +5004,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
       </font>
       <fill>
@@ -3787,6 +5015,25 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3798,6 +5045,25 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3820,6 +5086,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3830,6 +5126,33 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor indexed="64"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
       </font>
@@ -3842,14 +5165,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3924,36 +5239,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
       </font>
       <fill>
@@ -3965,1222 +5250,10 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFF0000"/>
       </font>
       <fill>
         <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor indexed="64"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor indexed="64"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -5424,49 +5497,49 @@
   </dxfs>
   <tableStyles count="9">
     <tableStyle name="MODELO LISTA DE COMPROBACION - -style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="308"/>
-      <tableStyleElement type="firstRowStripe" dxfId="307"/>
-      <tableStyleElement type="secondRowStripe" dxfId="306"/>
+      <tableStyleElement type="headerRow" dxfId="318"/>
+      <tableStyleElement type="firstRowStripe" dxfId="317"/>
+      <tableStyleElement type="secondRowStripe" dxfId="316"/>
     </tableStyle>
     <tableStyle name="MODELO LISTA DE COMPROBACION - -style 2" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="305"/>
-      <tableStyleElement type="firstRowStripe" dxfId="304"/>
-      <tableStyleElement type="secondRowStripe" dxfId="303"/>
+      <tableStyleElement type="headerRow" dxfId="315"/>
+      <tableStyleElement type="firstRowStripe" dxfId="314"/>
+      <tableStyleElement type="secondRowStripe" dxfId="313"/>
     </tableStyle>
     <tableStyle name="MODELO LISTA DE COMPROBACION - -style 3" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="headerRow" dxfId="302"/>
-      <tableStyleElement type="firstRowStripe" dxfId="301"/>
-      <tableStyleElement type="secondRowStripe" dxfId="300"/>
+      <tableStyleElement type="headerRow" dxfId="312"/>
+      <tableStyleElement type="firstRowStripe" dxfId="311"/>
+      <tableStyleElement type="secondRowStripe" dxfId="310"/>
     </tableStyle>
     <tableStyle name="MODELO LISTA DE COMPROBACION - -style 4" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="headerRow" dxfId="299"/>
-      <tableStyleElement type="firstRowStripe" dxfId="298"/>
-      <tableStyleElement type="secondRowStripe" dxfId="297"/>
+      <tableStyleElement type="headerRow" dxfId="309"/>
+      <tableStyleElement type="firstRowStripe" dxfId="308"/>
+      <tableStyleElement type="secondRowStripe" dxfId="307"/>
     </tableStyle>
     <tableStyle name="MODELO LISTA DE COMPROBACION - -style 5" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="headerRow" dxfId="296"/>
-      <tableStyleElement type="firstRowStripe" dxfId="295"/>
-      <tableStyleElement type="secondRowStripe" dxfId="294"/>
+      <tableStyleElement type="headerRow" dxfId="306"/>
+      <tableStyleElement type="firstRowStripe" dxfId="305"/>
+      <tableStyleElement type="secondRowStripe" dxfId="304"/>
     </tableStyle>
     <tableStyle name="MODELO LISTA DE COMPROBACION - -style 6" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="headerRow" dxfId="293"/>
-      <tableStyleElement type="firstRowStripe" dxfId="292"/>
-      <tableStyleElement type="secondRowStripe" dxfId="291"/>
+      <tableStyleElement type="headerRow" dxfId="303"/>
+      <tableStyleElement type="firstRowStripe" dxfId="302"/>
+      <tableStyleElement type="secondRowStripe" dxfId="301"/>
     </tableStyle>
     <tableStyle name="MODELO LISTA DE COMPROBACION - -style 7" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="headerRow" dxfId="290"/>
-      <tableStyleElement type="firstRowStripe" dxfId="289"/>
-      <tableStyleElement type="secondRowStripe" dxfId="288"/>
+      <tableStyleElement type="headerRow" dxfId="300"/>
+      <tableStyleElement type="firstRowStripe" dxfId="299"/>
+      <tableStyleElement type="secondRowStripe" dxfId="298"/>
     </tableStyle>
     <tableStyle name="MODELO LISTA DE COMPROBACION - -style 8" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
-      <tableStyleElement type="headerRow" dxfId="287"/>
-      <tableStyleElement type="firstRowStripe" dxfId="286"/>
-      <tableStyleElement type="secondRowStripe" dxfId="285"/>
+      <tableStyleElement type="headerRow" dxfId="297"/>
+      <tableStyleElement type="firstRowStripe" dxfId="296"/>
+      <tableStyleElement type="secondRowStripe" dxfId="295"/>
     </tableStyle>
     <tableStyle name="MODELO LISTA DE COMPROBACION - -style 9" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
-      <tableStyleElement type="headerRow" dxfId="284"/>
-      <tableStyleElement type="firstRowStripe" dxfId="283"/>
-      <tableStyleElement type="secondRowStripe" dxfId="282"/>
+      <tableStyleElement type="headerRow" dxfId="294"/>
+      <tableStyleElement type="firstRowStripe" dxfId="293"/>
+      <tableStyleElement type="secondRowStripe" dxfId="292"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -5483,7 +5556,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -5693,7 +5766,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -5903,7 +5976,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -7147,28 +7220,28 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="78"/>
     </row>
     <row r="4" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="78"/>
     </row>
     <row r="5" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="2"/>
@@ -7178,12 +7251,12 @@
       <c r="E5" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="78"/>
     </row>
     <row r="6" spans="2:11" ht="22.8" x14ac:dyDescent="0.3">
       <c r="C6" s="1"/>
@@ -7194,50 +7267,50 @@
       <c r="H6" s="85"/>
       <c r="I6" s="85"/>
       <c r="J6" s="85"/>
-      <c r="K6" s="80"/>
+      <c r="K6" s="86"/>
     </row>
     <row r="7" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="87" t="s">
+      <c r="B7" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="89" t="s">
+      <c r="C7" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="90"/>
-      <c r="E7" s="93" t="s">
+      <c r="D7" s="88"/>
+      <c r="E7" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="87" t="s">
+      <c r="F7" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="93" t="s">
+      <c r="G7" s="79" t="s">
         <v>6</v>
       </c>
       <c r="H7" s="5"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="87"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="81"/>
     </row>
     <row r="8" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B8" s="88"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="88"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
     </row>
     <row r="9" spans="2:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <v>1</v>
       </c>
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="80"/>
+      <c r="D9" s="86"/>
       <c r="E9" s="7" t="s">
         <v>9</v>
       </c>
@@ -7254,10 +7327,10 @@
       <c r="B10" s="6">
         <v>2</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="80"/>
+      <c r="D10" s="86"/>
       <c r="E10" s="7" t="s">
         <v>9</v>
       </c>
@@ -7273,10 +7346,10 @@
       <c r="B11" s="6">
         <v>3</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="80"/>
+      <c r="D11" s="86"/>
       <c r="E11" s="7" t="s">
         <v>9</v>
       </c>
@@ -7292,10 +7365,10 @@
       <c r="B12" s="6">
         <v>4</v>
       </c>
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="80"/>
+      <c r="D12" s="86"/>
       <c r="E12" s="7" t="s">
         <v>9</v>
       </c>
@@ -7311,10 +7384,10 @@
       <c r="B13" s="6">
         <v>5</v>
       </c>
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="80"/>
+      <c r="D13" s="86"/>
       <c r="E13" s="7" t="s">
         <v>9</v>
       </c>
@@ -7330,10 +7403,10 @@
       <c r="B14" s="6">
         <v>6</v>
       </c>
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="80"/>
+      <c r="D14" s="86"/>
       <c r="E14" s="7" t="s">
         <v>9</v>
       </c>
@@ -7349,10 +7422,10 @@
       <c r="B15" s="6">
         <v>7</v>
       </c>
-      <c r="C15" s="79" t="s">
+      <c r="C15" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="80"/>
+      <c r="D15" s="86"/>
       <c r="E15" s="12" t="s">
         <v>22</v>
       </c>
@@ -7368,10 +7441,10 @@
       <c r="B16" s="6">
         <v>8</v>
       </c>
-      <c r="C16" s="79" t="s">
+      <c r="C16" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="80"/>
+      <c r="D16" s="86"/>
       <c r="E16" s="12" t="s">
         <v>22</v>
       </c>
@@ -7387,10 +7460,10 @@
       <c r="B17" s="6">
         <v>9</v>
       </c>
-      <c r="C17" s="79" t="s">
+      <c r="C17" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="80"/>
+      <c r="D17" s="86"/>
       <c r="E17" s="7" t="s">
         <v>9</v>
       </c>
@@ -7406,10 +7479,10 @@
       <c r="B18" s="6">
         <v>10</v>
       </c>
-      <c r="C18" s="79" t="s">
+      <c r="C18" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="80"/>
+      <c r="D18" s="86"/>
       <c r="E18" s="7" t="s">
         <v>9</v>
       </c>
@@ -7425,10 +7498,10 @@
       <c r="B19" s="6">
         <v>11</v>
       </c>
-      <c r="C19" s="79" t="s">
+      <c r="C19" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="80"/>
+      <c r="D19" s="86"/>
       <c r="E19" s="7" t="s">
         <v>9</v>
       </c>
@@ -8825,18 +8898,6 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="C3:K4"/>
-    <mergeCell ref="E5:K5"/>
-    <mergeCell ref="F6:K6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
@@ -8847,6 +8908,18 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="C3:K4"/>
+    <mergeCell ref="E5:K5"/>
+    <mergeCell ref="F6:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.47" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
@@ -8883,28 +8956,28 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="78"/>
     </row>
     <row r="4" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="78"/>
     </row>
     <row r="5" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="2"/>
@@ -8914,12 +8987,12 @@
       <c r="E5" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="78"/>
     </row>
     <row r="6" spans="2:11" ht="22.8" x14ac:dyDescent="0.3">
       <c r="C6" s="1"/>
@@ -8930,16 +9003,16 @@
       <c r="H6" s="85"/>
       <c r="I6" s="85"/>
       <c r="J6" s="85"/>
-      <c r="K6" s="80"/>
+      <c r="K6" s="86"/>
     </row>
     <row r="7" spans="2:11" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="80"/>
+      <c r="D7" s="86"/>
       <c r="E7" s="15" t="s">
         <v>6</v>
       </c>
@@ -8964,10 +9037,10 @@
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="79" t="s">
+      <c r="C8" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="80"/>
+      <c r="D8" s="86"/>
       <c r="E8" s="76" t="s">
         <v>9</v>
       </c>
@@ -8992,10 +9065,10 @@
       <c r="B9" s="6">
         <v>2</v>
       </c>
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="80"/>
+      <c r="D9" s="86"/>
       <c r="E9" s="63" t="s">
         <v>9</v>
       </c>
@@ -9019,10 +9092,10 @@
       <c r="B10" s="6">
         <v>3</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="80"/>
+      <c r="D10" s="86"/>
       <c r="E10" s="63" t="s">
         <v>9</v>
       </c>
@@ -9046,10 +9119,10 @@
       <c r="B11" s="6">
         <v>4</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="80"/>
+      <c r="D11" s="86"/>
       <c r="E11" s="62" t="s">
         <v>22</v>
       </c>
@@ -9073,10 +9146,10 @@
       <c r="B12" s="6">
         <v>5</v>
       </c>
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="80"/>
+      <c r="D12" s="86"/>
       <c r="E12" s="63" t="s">
         <v>9</v>
       </c>
@@ -9100,10 +9173,10 @@
       <c r="B13" s="6">
         <v>6</v>
       </c>
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="80"/>
+      <c r="D13" s="86"/>
       <c r="E13" s="63" t="s">
         <v>9</v>
       </c>
@@ -9127,10 +9200,10 @@
       <c r="B14" s="6">
         <v>7</v>
       </c>
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="80"/>
+      <c r="D14" s="86"/>
       <c r="E14" s="63" t="s">
         <v>9</v>
       </c>
@@ -9154,10 +9227,10 @@
       <c r="B15" s="6">
         <v>8</v>
       </c>
-      <c r="C15" s="79" t="s">
+      <c r="C15" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="80"/>
+      <c r="D15" s="86"/>
       <c r="E15" s="63" t="s">
         <v>9</v>
       </c>
@@ -9181,10 +9254,10 @@
       <c r="B16" s="6">
         <v>9</v>
       </c>
-      <c r="C16" s="79" t="s">
+      <c r="C16" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="80"/>
+      <c r="D16" s="86"/>
       <c r="E16" s="63" t="s">
         <v>9</v>
       </c>
@@ -9208,10 +9281,10 @@
       <c r="B17" s="6">
         <v>10</v>
       </c>
-      <c r="C17" s="79" t="s">
+      <c r="C17" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="80"/>
+      <c r="D17" s="86"/>
       <c r="E17" s="63" t="s">
         <v>9</v>
       </c>
@@ -9235,10 +9308,10 @@
       <c r="B18" s="6">
         <v>11</v>
       </c>
-      <c r="C18" s="79" t="s">
+      <c r="C18" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="80"/>
+      <c r="D18" s="86"/>
       <c r="E18" s="63" t="s">
         <v>9</v>
       </c>
@@ -10691,31 +10764,31 @@
       <c r="A1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="94" t="s">
+      <c r="B1" s="106" t="s">
         <v>99</v>
       </c>
       <c r="C1" s="85"/>
-      <c r="D1" s="80"/>
+      <c r="D1" s="86"/>
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
       <c r="G1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="94" t="s">
+      <c r="H1" s="106" t="s">
         <v>99</v>
       </c>
       <c r="I1" s="85"/>
-      <c r="J1" s="80"/>
+      <c r="J1" s="86"/>
       <c r="K1" s="17"/>
       <c r="L1" s="17"/>
       <c r="M1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="94" t="s">
+      <c r="N1" s="106" t="s">
         <v>99</v>
       </c>
       <c r="O1" s="85"/>
-      <c r="P1" s="80"/>
+      <c r="P1" s="86"/>
       <c r="Q1" s="17"/>
       <c r="R1" s="17"/>
       <c r="S1" s="17"/>
@@ -10732,27 +10805,27 @@
       <c r="A2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="98">
+      <c r="B2" s="107">
         <v>46296</v>
       </c>
       <c r="C2" s="85"/>
-      <c r="D2" s="80"/>
+      <c r="D2" s="86"/>
       <c r="G2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="98">
+      <c r="H2" s="107">
         <v>46296</v>
       </c>
       <c r="I2" s="85"/>
-      <c r="J2" s="80"/>
+      <c r="J2" s="86"/>
       <c r="M2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="98">
+      <c r="N2" s="107">
         <v>46296</v>
       </c>
       <c r="O2" s="85"/>
-      <c r="P2" s="80"/>
+      <c r="P2" s="86"/>
     </row>
     <row r="3" spans="1:27" ht="31.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="18" t="s">
@@ -10762,7 +10835,7 @@
         <v>76</v>
       </c>
       <c r="C3" s="85"/>
-      <c r="D3" s="80"/>
+      <c r="D3" s="86"/>
       <c r="G3" s="18" t="s">
         <v>33</v>
       </c>
@@ -10770,7 +10843,7 @@
         <v>76</v>
       </c>
       <c r="I3" s="85"/>
-      <c r="J3" s="80"/>
+      <c r="J3" s="86"/>
       <c r="M3" s="18" t="s">
         <v>33</v>
       </c>
@@ -10778,64 +10851,64 @@
         <v>76</v>
       </c>
       <c r="O3" s="85"/>
-      <c r="P3" s="80"/>
+      <c r="P3" s="86"/>
     </row>
     <row r="4" spans="1:27" ht="46.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="104" t="s">
+      <c r="A4" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="80"/>
+      <c r="B4" s="86"/>
       <c r="C4" s="101" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="80"/>
-      <c r="G4" s="97" t="s">
+      <c r="D4" s="86"/>
+      <c r="G4" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="80"/>
-      <c r="I4" s="96" t="s">
+      <c r="H4" s="86"/>
+      <c r="I4" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="80"/>
-      <c r="M4" s="97" t="s">
+      <c r="J4" s="86"/>
+      <c r="M4" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="80"/>
-      <c r="O4" s="96" t="s">
+      <c r="N4" s="86"/>
+      <c r="O4" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="P4" s="80"/>
+      <c r="P4" s="86"/>
     </row>
     <row r="5" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
-      <c r="J5" s="105"/>
-      <c r="K5" s="82"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="78"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
     </row>
     <row r="6" spans="1:27" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A6" s="102" t="s">
+      <c r="A6" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="G6" s="103" t="s">
+      <c r="B6" s="78"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
+      <c r="G6" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="M6" s="103" t="s">
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
+      <c r="M6" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="82"/>
-      <c r="O6" s="82"/>
-      <c r="P6" s="82"/>
+      <c r="N6" s="78"/>
+      <c r="O6" s="78"/>
+      <c r="P6" s="78"/>
     </row>
     <row r="7" spans="1:27" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
@@ -11164,10 +11237,10 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="82"/>
+      <c r="B17" s="78"/>
       <c r="C17" s="9">
         <f>COUNTA(C8:C16)</f>
         <v>7</v>
@@ -11176,10 +11249,10 @@
         <f>COUNTA(D8:D16)</f>
         <v>2</v>
       </c>
-      <c r="G17" s="100" t="s">
+      <c r="G17" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="H17" s="82"/>
+      <c r="H17" s="78"/>
       <c r="I17" s="37">
         <f>COUNTA(I8:I16)</f>
         <v>6</v>
@@ -11188,10 +11261,10 @@
         <f>COUNTA(J8:J16)</f>
         <v>3</v>
       </c>
-      <c r="M17" s="100" t="s">
+      <c r="M17" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="N17" s="82"/>
+      <c r="N17" s="78"/>
       <c r="O17" s="37">
         <f>COUNTA(O8:O16)</f>
         <v>7</v>
@@ -11202,10 +11275,10 @@
       </c>
     </row>
     <row r="18" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="82"/>
+      <c r="B18" s="78"/>
       <c r="C18" s="69">
         <f t="shared" ref="C18:D18" si="0">C17/9</f>
         <v>0.77777777777777779</v>
@@ -11214,10 +11287,10 @@
         <f t="shared" si="0"/>
         <v>0.22222222222222221</v>
       </c>
-      <c r="G18" s="100" t="s">
+      <c r="G18" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="H18" s="82"/>
+      <c r="H18" s="78"/>
       <c r="I18" s="75">
         <f t="shared" ref="I18:J18" si="1">I17/9</f>
         <v>0.66666666666666663</v>
@@ -11226,10 +11299,10 @@
         <f t="shared" si="1"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M18" s="100" t="s">
+      <c r="M18" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="N18" s="82"/>
+      <c r="N18" s="78"/>
       <c r="O18" s="75">
         <f t="shared" ref="O18:P18" si="2">O17/9</f>
         <v>0.77777777777777779</v>
@@ -11254,24 +11327,24 @@
       <c r="P19" s="9"/>
     </row>
     <row r="20" spans="1:16" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="107"/>
-      <c r="C20" s="107"/>
-      <c r="D20" s="107"/>
-      <c r="G20" s="108" t="s">
+      <c r="B20" s="94"/>
+      <c r="C20" s="94"/>
+      <c r="D20" s="94"/>
+      <c r="G20" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="107"/>
-      <c r="I20" s="107"/>
-      <c r="J20" s="107"/>
-      <c r="M20" s="108" t="s">
+      <c r="H20" s="94"/>
+      <c r="I20" s="94"/>
+      <c r="J20" s="94"/>
+      <c r="M20" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="N20" s="107"/>
-      <c r="O20" s="107"/>
-      <c r="P20" s="107"/>
+      <c r="N20" s="94"/>
+      <c r="O20" s="94"/>
+      <c r="P20" s="94"/>
     </row>
     <row r="21" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="39" t="s">
@@ -11472,10 +11545,10 @@
       <c r="P26" s="74"/>
     </row>
     <row r="27" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A27" s="99" t="s">
+      <c r="A27" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="82"/>
+      <c r="B27" s="78"/>
       <c r="C27" s="9">
         <f>COUNTA(C22:C26)</f>
         <v>5</v>
@@ -11484,10 +11557,10 @@
         <f>COUNTA(D22:D26)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="100" t="s">
+      <c r="G27" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="H27" s="82"/>
+      <c r="H27" s="78"/>
       <c r="I27" s="37">
         <f>COUNTA(I22:I26)</f>
         <v>4</v>
@@ -11496,10 +11569,10 @@
         <f>COUNTA(J22:J26)</f>
         <v>1</v>
       </c>
-      <c r="M27" s="100" t="s">
+      <c r="M27" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="N27" s="82"/>
+      <c r="N27" s="78"/>
       <c r="O27" s="37">
         <f>COUNTA(O22:O26)</f>
         <v>4</v>
@@ -11510,10 +11583,10 @@
       </c>
     </row>
     <row r="28" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="82"/>
+      <c r="B28" s="78"/>
       <c r="C28" s="69">
         <f t="shared" ref="C28:D28" si="3">C27/5</f>
         <v>1</v>
@@ -11522,10 +11595,10 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G28" s="100" t="s">
+      <c r="G28" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="H28" s="82"/>
+      <c r="H28" s="78"/>
       <c r="I28" s="75">
         <f t="shared" ref="I28:J28" si="4">I27/5</f>
         <v>0.8</v>
@@ -11534,10 +11607,10 @@
         <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
-      <c r="M28" s="100" t="s">
+      <c r="M28" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="N28" s="82"/>
+      <c r="N28" s="78"/>
       <c r="O28" s="75">
         <f t="shared" ref="O28:P28" si="5">O27/5</f>
         <v>0.8</v>
@@ -11562,24 +11635,24 @@
       <c r="P29" s="9"/>
     </row>
     <row r="30" spans="1:16" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A30" s="102" t="s">
+      <c r="A30" s="103" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="82"/>
-      <c r="C30" s="82"/>
-      <c r="D30" s="82"/>
-      <c r="G30" s="103" t="s">
+      <c r="B30" s="78"/>
+      <c r="C30" s="78"/>
+      <c r="D30" s="78"/>
+      <c r="G30" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="H30" s="82"/>
-      <c r="I30" s="82"/>
-      <c r="J30" s="82"/>
-      <c r="M30" s="103" t="s">
+      <c r="H30" s="78"/>
+      <c r="I30" s="78"/>
+      <c r="J30" s="78"/>
+      <c r="M30" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="N30" s="82"/>
-      <c r="O30" s="82"/>
-      <c r="P30" s="82"/>
+      <c r="N30" s="78"/>
+      <c r="O30" s="78"/>
+      <c r="P30" s="78"/>
     </row>
     <row r="31" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A31" s="39" t="s">
@@ -11626,7 +11699,7 @@
       <c r="B32" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="C32" s="77" t="s">
+      <c r="C32" s="33" t="s">
         <v>40</v>
       </c>
       <c r="D32" s="33"/>
@@ -11658,7 +11731,7 @@
       <c r="B33" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="C33" s="78" t="s">
+      <c r="C33" s="33" t="s">
         <v>40</v>
       </c>
       <c r="D33" s="33"/>
@@ -11690,7 +11763,7 @@
       <c r="B34" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="77" t="s">
+      <c r="C34" s="33" t="s">
         <v>40</v>
       </c>
       <c r="D34" s="33"/>
@@ -11716,10 +11789,10 @@
       <c r="P34" s="33"/>
     </row>
     <row r="35" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A35" s="99" t="s">
+      <c r="A35" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="82"/>
+      <c r="B35" s="78"/>
       <c r="C35" s="9">
         <f>COUNTA(C32:C34)</f>
         <v>3</v>
@@ -11728,10 +11801,10 @@
         <f>COUNTA(D32:D34)</f>
         <v>0</v>
       </c>
-      <c r="G35" s="100" t="s">
+      <c r="G35" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="H35" s="82"/>
+      <c r="H35" s="78"/>
       <c r="I35" s="37">
         <f>COUNTA(I32:I34)</f>
         <v>3</v>
@@ -11740,10 +11813,10 @@
         <f>COUNTA(J32:J34)</f>
         <v>0</v>
       </c>
-      <c r="M35" s="100" t="s">
+      <c r="M35" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="N35" s="82"/>
+      <c r="N35" s="78"/>
       <c r="O35" s="37">
         <f>COUNTA(O32:O34)</f>
         <v>3</v>
@@ -11754,10 +11827,10 @@
       </c>
     </row>
     <row r="36" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A36" s="99" t="s">
+      <c r="A36" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="82"/>
+      <c r="B36" s="78"/>
       <c r="C36" s="69">
         <f t="shared" ref="C36:D36" si="6">C35/3</f>
         <v>1</v>
@@ -11766,10 +11839,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G36" s="100" t="s">
+      <c r="G36" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="H36" s="82"/>
+      <c r="H36" s="78"/>
       <c r="I36" s="75">
         <f t="shared" ref="I36:J36" si="7">I35/3</f>
         <v>1</v>
@@ -11778,10 +11851,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M36" s="100" t="s">
+      <c r="M36" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="N36" s="82"/>
+      <c r="N36" s="78"/>
       <c r="O36" s="75">
         <f t="shared" ref="O36:P36" si="8">O35/3</f>
         <v>1</v>
@@ -11822,21 +11895,21 @@
       <c r="P39" s="9"/>
     </row>
     <row r="40" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A40" s="95" t="s">
+      <c r="A40" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="B40" s="82"/>
-      <c r="C40" s="82"/>
-      <c r="G40" s="95" t="s">
+      <c r="B40" s="78"/>
+      <c r="C40" s="78"/>
+      <c r="G40" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="H40" s="82"/>
-      <c r="I40" s="82"/>
+      <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
       <c r="J40" s="9"/>
-      <c r="N40" s="95" t="s">
+      <c r="N40" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="O40" s="82"/>
+      <c r="O40" s="78"/>
       <c r="P40" s="9"/>
     </row>
     <row r="41" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
@@ -12885,20 +12958,22 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="M20:P20"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="G28:H28"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="H2:J2"/>
@@ -12915,1031 +12990,1079 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="M30:P30"/>
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="M20:P20"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="G17:H17"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
-    <cfRule type="containsText" dxfId="281" priority="330" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="291" priority="348" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="280" priority="329" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="290" priority="347" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="279" priority="327" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="289" priority="346" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="278" priority="328" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="288" priority="345" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:C9">
-    <cfRule type="containsText" dxfId="277" priority="324" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="287" priority="342" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="276" priority="323" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="286" priority="341" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="containsText" dxfId="275" priority="321" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="285" priority="340" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C9))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="274" priority="322" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="284" priority="339" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C9))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C10">
-    <cfRule type="containsText" dxfId="273" priority="318" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="283" priority="336" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C9))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="272" priority="317" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="282" priority="335" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C9))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="containsText" dxfId="271" priority="314" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="281" priority="331" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C10))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="270" priority="316" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="280" priority="333" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C10))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="269" priority="315" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="279" priority="332" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C10))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="268" priority="313" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="278" priority="334" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C10))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11 I11 O11 I14 C16 I16 O16 I25 O25 C32:C34">
-    <cfRule type="cellIs" dxfId="267" priority="331" operator="equal">
+  <conditionalFormatting sqref="C11 I11 O11 I14 C16 I16 O16 I25 O25">
+    <cfRule type="cellIs" dxfId="277" priority="349" operator="equal">
       <formula>"X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="containsText" dxfId="266" priority="303" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="276" priority="324" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C12))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="265" priority="304" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="275" priority="322" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C12))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="264" priority="305" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="274" priority="321" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C12))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="263" priority="306" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="273" priority="323" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C12))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:C13">
-    <cfRule type="containsText" dxfId="262" priority="299" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="272" priority="317" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C12))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="261" priority="300" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="271" priority="318" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C12))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="containsText" dxfId="260" priority="298" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="270" priority="315" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C13))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="259" priority="297" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="269" priority="316" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C13))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C14">
-    <cfRule type="containsText" dxfId="258" priority="293" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="268" priority="312" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C13))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="257" priority="294" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="267" priority="311" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C13))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="containsText" dxfId="256" priority="292" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="266" priority="310" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C14))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="255" priority="291" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="265" priority="309" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C14))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:C15">
-    <cfRule type="containsText" dxfId="254" priority="287" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="264" priority="305" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C14))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="253" priority="288" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="263" priority="306" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C14))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="containsText" dxfId="252" priority="283" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="262" priority="304" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="251" priority="284" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="261" priority="303" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="250" priority="286" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="260" priority="302" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="249" priority="285" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="259" priority="301" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C15))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22">
-    <cfRule type="containsText" dxfId="248" priority="275" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="258" priority="292" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="247" priority="276" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="257" priority="291" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="246" priority="274" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="256" priority="293" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="245" priority="273" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="255" priority="294" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:C23">
-    <cfRule type="containsText" dxfId="244" priority="270" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="254" priority="287" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="243" priority="269" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="253" priority="288" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C23">
-    <cfRule type="containsText" dxfId="242" priority="268" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="252" priority="285" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C23))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="241" priority="267" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="251" priority="286" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C23))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C23:C24">
-    <cfRule type="containsText" dxfId="240" priority="264" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="250" priority="281" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C23))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="239" priority="263" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="249" priority="282" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C23))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24">
-    <cfRule type="containsText" dxfId="238" priority="262" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="248" priority="280" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C24))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="237" priority="261" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="247" priority="279" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C24))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C25">
-    <cfRule type="containsText" dxfId="236" priority="258" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="246" priority="276" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C24))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="235" priority="257" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="245" priority="275" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C24))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25">
-    <cfRule type="containsText" dxfId="234" priority="256" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="244" priority="273" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C25))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="233" priority="255" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="243" priority="274" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C25))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:C26">
-    <cfRule type="containsText" dxfId="232" priority="252" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="242" priority="270" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C25))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="231" priority="251" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="241" priority="269" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C25))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26">
-    <cfRule type="containsText" dxfId="230" priority="249" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="240" priority="268" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="229" priority="248" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="239" priority="267" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="228" priority="247" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="238" priority="266" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="227" priority="250" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="237" priority="265" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C26))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D10 J8:J10 P8:P10 J12:J13 D12:D15 P12:P15 J15 J22:J24 P22:P24 D22:D26 J26 P26">
-    <cfRule type="cellIs" dxfId="226" priority="332" operator="equal">
+    <cfRule type="cellIs" dxfId="236" priority="350" operator="equal">
       <formula>"X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11">
-    <cfRule type="containsText" dxfId="225" priority="312" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="235" priority="328" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="224" priority="311" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="234" priority="325" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="223" priority="310" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="233" priority="326" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="222" priority="309" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="232" priority="327" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="221" priority="308" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="231" priority="329" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="220" priority="307" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="230" priority="330" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D11))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16">
-    <cfRule type="containsText" dxfId="219" priority="280" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="229" priority="296" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="218" priority="279" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="228" priority="297" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="217" priority="282" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="227" priority="298" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="216" priority="281" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="226" priority="299" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="215" priority="277" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="225" priority="295" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="214" priority="278" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="224" priority="300" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D16))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32:D34">
-    <cfRule type="containsText" dxfId="213" priority="245" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="223" priority="264" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="212" priority="246" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="222" priority="263" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="211" priority="243" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="221" priority="262" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="210" priority="241" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="220" priority="261" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="209" priority="244" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="219" priority="260" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="208" priority="242" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="218" priority="259" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D32))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="207" priority="88" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="217" priority="105" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I8))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="206" priority="87" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="216" priority="106" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I8))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="205" priority="89" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="215" priority="107" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I8))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="204" priority="90" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="214" priority="108" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:I9">
-    <cfRule type="containsText" dxfId="203" priority="83" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="213" priority="101" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I8))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="202" priority="84" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="212" priority="102" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9">
-    <cfRule type="containsText" dxfId="201" priority="82" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="211" priority="99" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I9))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="200" priority="81" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="210" priority="100" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I9))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I10">
-    <cfRule type="containsText" dxfId="199" priority="78" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="209" priority="96" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I9))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="198" priority="77" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="208" priority="95" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I9))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10">
-    <cfRule type="containsText" dxfId="197" priority="75" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="207" priority="91" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I10))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="196" priority="74" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="206" priority="94" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I10))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="195" priority="76" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="205" priority="93" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I10))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="194" priority="73" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="204" priority="92" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I10))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="193" priority="65" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="203" priority="83" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I12))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="192" priority="64" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="202" priority="81" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I12))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="191" priority="63" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="201" priority="82" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I12))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="190" priority="66" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="200" priority="84" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12:I13">
-    <cfRule type="containsText" dxfId="189" priority="60" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="199" priority="77" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I12))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="188" priority="59" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="198" priority="78" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="187" priority="58" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="197" priority="73" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I13))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="186" priority="57" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="196" priority="74" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I13))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="185" priority="56" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="195" priority="75" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I13))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="184" priority="55" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="194" priority="76" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="183" priority="54" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="193" priority="72" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="182" priority="49" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="192" priority="71" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="181" priority="50" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="191" priority="70" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="180" priority="51" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="190" priority="69" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="179" priority="52" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="189" priority="67" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="178" priority="53" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="188" priority="68" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I15))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="containsText" dxfId="177" priority="174" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="187" priority="189" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I22))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="176" priority="173" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="186" priority="190" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I22))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="175" priority="172" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="185" priority="192" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I22))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="174" priority="171" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="184" priority="191" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I23">
-    <cfRule type="containsText" dxfId="173" priority="167" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="183" priority="186" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I22))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="172" priority="168" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="182" priority="185" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23">
-    <cfRule type="containsText" dxfId="171" priority="165" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="181" priority="183" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I23))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="170" priority="166" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="180" priority="184" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I23))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23:I24">
-    <cfRule type="containsText" dxfId="169" priority="161" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="179" priority="180" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I23))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="168" priority="162" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="178" priority="179" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I23))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24">
-    <cfRule type="containsText" dxfId="167" priority="157" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="177" priority="176" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I24))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="166" priority="158" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="176" priority="178" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I24))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="165" priority="159" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="175" priority="177" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I24))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="164" priority="160" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="174" priority="175" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I24))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26">
-    <cfRule type="containsText" dxfId="163" priority="151" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="173" priority="173" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="162" priority="152" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="172" priority="169" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="161" priority="153" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="171" priority="170" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="160" priority="154" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="170" priority="171" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="159" priority="156" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="169" priority="172" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="158" priority="155" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="168" priority="174" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(I26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I32">
+    <cfRule type="containsText" dxfId="167" priority="53" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="166" priority="54" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="165" priority="51" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="164" priority="52" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I32:I33">
+    <cfRule type="containsText" dxfId="163" priority="47" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="162" priority="48" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I33">
+    <cfRule type="containsText" dxfId="161" priority="45" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I33))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="160" priority="46" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I33:I34">
+    <cfRule type="containsText" dxfId="159" priority="41" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I33))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="158" priority="42" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I34">
+    <cfRule type="containsText" dxfId="157" priority="39" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I34))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="156" priority="37" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I34))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="155" priority="38" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I34))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="154" priority="40" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(I34))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11">
-    <cfRule type="containsText" dxfId="157" priority="72" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="153" priority="89" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="156" priority="71" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="152" priority="88" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="155" priority="70" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="151" priority="87" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="154" priority="69" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="150" priority="86" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="153" priority="68" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="149" priority="85" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="152" priority="67" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="148" priority="90" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J11))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="151" priority="47" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="147" priority="66" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J14))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="150" priority="46" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="146" priority="65" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J14))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="149" priority="45" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="145" priority="64" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J14))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="148" priority="44" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="144" priority="63" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J14))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="147" priority="43" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="143" priority="62" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J14))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="146" priority="48" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="142" priority="61" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J14))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16">
-    <cfRule type="containsText" dxfId="145" priority="38" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="141" priority="60" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="144" priority="39" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="140" priority="59" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="143" priority="40" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="139" priority="58" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="142" priority="41" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="138" priority="56" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="141" priority="42" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="137" priority="55" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="140" priority="37" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="136" priority="57" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J16))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J25">
-    <cfRule type="containsText" dxfId="139" priority="145" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="135" priority="166" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J25))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="138" priority="150" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="134" priority="165" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J25))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="137" priority="149" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="133" priority="164" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J25))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="136" priority="148" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="132" priority="168" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J25))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="135" priority="147" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="131" priority="163" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J25))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="134" priority="146" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="130" priority="167" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J25))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J32">
-    <cfRule type="containsText" dxfId="133" priority="237" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="129" priority="257" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="132" priority="238" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="128" priority="258" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="131" priority="239" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="127" priority="255" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="130" priority="240" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="126" priority="256" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J32))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J32:J33">
-    <cfRule type="containsText" dxfId="129" priority="234" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="125" priority="251" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="128" priority="233" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="124" priority="252" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J32))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J33">
-    <cfRule type="containsText" dxfId="127" priority="231" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="123" priority="250" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J33))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="126" priority="232" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="122" priority="249" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J33))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J33:J34">
-    <cfRule type="containsText" dxfId="125" priority="228" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="121" priority="246" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J33))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="124" priority="227" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="120" priority="245" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J33))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J34">
-    <cfRule type="containsText" dxfId="123" priority="224" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="119" priority="243" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J34))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="122" priority="226" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="118" priority="244" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J34))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="121" priority="225" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="117" priority="242" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J34))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="120" priority="223" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="116" priority="241" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(J34))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O8">
-    <cfRule type="containsText" dxfId="119" priority="91" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="115" priority="110" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O8))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="118" priority="92" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="114" priority="109" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O8))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="117" priority="93" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="113" priority="111" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O8))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="116" priority="94" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="112" priority="112" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O8:O9">
-    <cfRule type="containsText" dxfId="115" priority="96" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="111" priority="113" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O8))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="114" priority="95" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="110" priority="114" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9">
-    <cfRule type="containsText" dxfId="113" priority="99" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="109" priority="117" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O9))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="112" priority="100" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="108" priority="118" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O9))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:O10">
-    <cfRule type="containsText" dxfId="111" priority="102" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="107" priority="119" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O9))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="110" priority="101" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="106" priority="120" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O9))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O10">
-    <cfRule type="containsText" dxfId="109" priority="106" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="105" priority="126" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O10))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="108" priority="108" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="104" priority="125" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O10))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="107" priority="107" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="103" priority="123" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O10))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="106" priority="105" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="102" priority="124" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O10))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O12">
-    <cfRule type="containsText" dxfId="105" priority="118" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="101" priority="136" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O12))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="104" priority="117" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="100" priority="134" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O12))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="103" priority="116" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="99" priority="135" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O12))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="102" priority="115" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="98" priority="133" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O12))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O12:O13">
-    <cfRule type="containsText" dxfId="101" priority="120" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="97" priority="137" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O12))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="100" priority="119" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="96" priority="138" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O12))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O13">
-    <cfRule type="containsText" dxfId="99" priority="124" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="95" priority="141" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O13))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="98" priority="123" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="94" priority="142" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O13))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O13:O14">
-    <cfRule type="containsText" dxfId="97" priority="125" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="93" priority="144" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O13))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="96" priority="126" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="92" priority="143" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O13))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O14">
-    <cfRule type="containsText" dxfId="95" priority="129" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="91" priority="147" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O14))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="94" priority="130" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="90" priority="148" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O14))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O14:O15">
-    <cfRule type="containsText" dxfId="93" priority="131" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="89" priority="150" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O14))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="92" priority="132" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="88" priority="149" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O14))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O15">
-    <cfRule type="containsText" dxfId="91" priority="141" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="87" priority="161" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="90" priority="142" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="86" priority="159" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="89" priority="143" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="85" priority="160" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="144" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="84" priority="162" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O15))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O22">
-    <cfRule type="containsText" dxfId="87" priority="175" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="83" priority="194" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O22))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="86" priority="178" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="82" priority="196" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O22))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="177" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="81" priority="195" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O22))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="176" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="80" priority="193" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O22:O23">
-    <cfRule type="containsText" dxfId="83" priority="180" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="79" priority="197" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O22))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="179" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="78" priority="198" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O23">
-    <cfRule type="containsText" dxfId="81" priority="183" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="77" priority="201" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O23))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="80" priority="184" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="76" priority="202" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O23))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O23:O24">
-    <cfRule type="containsText" dxfId="79" priority="185" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="75" priority="203" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O23))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="186" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="74" priority="204" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O23))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O24">
-    <cfRule type="containsText" dxfId="77" priority="189" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="73" priority="209" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O24))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="192" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="72" priority="210" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O24))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="190" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="71" priority="207" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O24))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="191" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="70" priority="208" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O24))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O26">
-    <cfRule type="containsText" dxfId="73" priority="199" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="69" priority="222" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="201" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="68" priority="217" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="71" priority="200" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="67" priority="218" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="70" priority="204" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="66" priority="219" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="69" priority="203" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="65" priority="220" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O26))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="202" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="64" priority="221" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(O26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O32">
+    <cfRule type="containsText" dxfId="63" priority="35" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="62" priority="36" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="61" priority="33" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="60" priority="34" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O32:O33">
+    <cfRule type="containsText" dxfId="59" priority="29" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="58" priority="30" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O33">
+    <cfRule type="containsText" dxfId="57" priority="27" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O33))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="56" priority="28" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O33:O34">
+    <cfRule type="containsText" dxfId="55" priority="23" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O33))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="54" priority="24" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O34">
+    <cfRule type="containsText" dxfId="53" priority="21" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O34))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="52" priority="19" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O34))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="51" priority="20" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O34))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="50" priority="22" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(O34))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P11">
-    <cfRule type="containsText" dxfId="67" priority="114" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="49" priority="131" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="110" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="48" priority="129" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="109" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="47" priority="132" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="113" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="46" priority="127" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="63" priority="112" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="45" priority="128" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P11))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="111" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="44" priority="130" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P11))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P16">
-    <cfRule type="containsText" dxfId="61" priority="134" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="43" priority="154" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="137" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="42" priority="151" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="138" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="41" priority="152" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="133" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="40" priority="155" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="135" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="39" priority="156" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="136" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="38" priority="153" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P16))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P25">
-    <cfRule type="containsText" dxfId="55" priority="196" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="37" priority="216" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P25))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="198" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="36" priority="215" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P25))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="195" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="35" priority="214" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P25))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="194" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="34" priority="213" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P25))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="193" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="33" priority="212" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P25))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="197" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="32" priority="211" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P25))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P32">
-    <cfRule type="containsText" dxfId="49" priority="220" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="31" priority="239" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="219" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="30" priority="237" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="47" priority="221" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="29" priority="238" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="222" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="28" priority="240" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P32))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P32:P33">
-    <cfRule type="containsText" dxfId="45" priority="216" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="27" priority="233" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="215" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="26" priority="234" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P32))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P33">
-    <cfRule type="containsText" dxfId="43" priority="214" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="25" priority="232" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P33))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="213" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="24" priority="231" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P33))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P33:P34">
-    <cfRule type="containsText" dxfId="41" priority="209" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="23" priority="227" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P33))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="210" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="22" priority="228" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P33))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P34">
-    <cfRule type="containsText" dxfId="39" priority="206" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="21" priority="226" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P34))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="205" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="20" priority="225" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P34))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="207" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="19" priority="224" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P34))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="208" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="18" priority="223" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(P34))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I32">
-    <cfRule type="containsText" dxfId="35" priority="31" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="32" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="33" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="34" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="35" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="36" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I32))))</formula>
+  <conditionalFormatting sqref="C32">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C32))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I33">
-    <cfRule type="containsText" dxfId="29" priority="25" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="26" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="27" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="28" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="29" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="30" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I33))))</formula>
+  <conditionalFormatting sqref="C32">
+    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="14" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="16" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C32))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I34">
-    <cfRule type="containsText" dxfId="23" priority="19" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I34))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="20" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I34))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I34))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I34))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I34))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(I34))))</formula>
+  <conditionalFormatting sqref="C33">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C33))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C33))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O32">
-    <cfRule type="containsText" dxfId="17" priority="13" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="14" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="17" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="18" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O32))))</formula>
+  <conditionalFormatting sqref="C33">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C33))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C33))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C33))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C33))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O33">
-    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="12" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O33))))</formula>
+  <conditionalFormatting sqref="C34">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C34))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C34))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O34">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O34))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O34))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O34))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O34))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O34))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH(("X"),(O34))))</formula>
+  <conditionalFormatting sqref="C34">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C34))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C34))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C34))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="X">
+      <formula>NOT(ISERROR(SEARCH(("X"),(C34))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13971,10 +14094,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="82"/>
+      <c r="B1" s="78"/>
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="59" t="s">
@@ -14001,10 +14124,10 @@
       </c>
     </row>
     <row r="9" spans="1:2" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="109" t="s">
+      <c r="A9" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="82"/>
+      <c r="B9" s="78"/>
     </row>
     <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="59" t="s">
@@ -14031,10 +14154,10 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="109" t="s">
+      <c r="A17" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="82"/>
+      <c r="B17" s="78"/>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="59" t="s">
